--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-021_有効休暇種別一覧取得_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-021_有効休暇種別一覧取得_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="6257925"/>
+    <ext cx="8572500" cy="6457950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-021 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-021 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="79" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -1709,7 +1709,8 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：未認証・トークン不正を 401 / E-001 の JSON（AuthenticationEntryPoint）に更新</t>
+          <t>・確定設計変更 D1〜D10 を反映：未認証・トークン不正を 401 / E-001 の JSON（AuthenticationEntryPoint）に更新
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -3374,7 +3375,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>@RequestParam / @PathVariable / Jwt を一切持たない。ユーザー個別のデータを返さないため userId も不要。
+          <t>@RequestParam / @PathVariable / Authentication を一切持たない。ユーザー個別のデータを返さないため userId も不要。
 管理者用 AdminLeaveTypeController（/api/admin/leave-types、ADMIN 限定）とはパスもクラスも分離する。
 コンストラクタインジェクション。</t>
         </is>
